--- a/XBRL-template-MPERS/backup-originals/Group/09-SOCIE.xlsx
+++ b/XBRL-template-MPERS/backup-originals/Group/09-SOCIE.xlsx
@@ -417,12 +417,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:A97"/>
+  <dimension ref="A1:D97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>01/01/YYYY - 31/12/YYYY</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
@@ -433,154 +447,162 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Disclosure of changes in equity [abstract]</t>
+          <t>Disclosure of changes in equity</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Statement of changes in equity [abstract]</t>
+          <t>Statement of changes in equity</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Statement of changes in equity [table]</t>
+          <t>Equity at beginning of period</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Consolidated and separate financial statements [axis]</t>
+          <t>Impact of changes in accounting policies</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Group [member]</t>
+          <t>Equity at beginning of period, restated</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Company [member]</t>
+          <t>Changes in equity</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Components of equity [axis]</t>
+          <t>Comprehensive income</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Equity [member]</t>
+          <t>Profit (loss)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Equity attributable to owners of parent [member]</t>
+          <t>Total other comprehensive income</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Issued capital [member]</t>
-        </is>
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>*Total comprehensive income</t>
+        </is>
+      </c>
+      <c r="B13">
+        <f>1*B11+1*B12</f>
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Retained earnings [member]</t>
+          <t>Contributions by and distributions to owners</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Treasury shares [member]</t>
+          <t>Acquisition (dilution) of equity interest in subsidiaries</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Reserves [Member]</t>
+          <t>Arising from conversion of Irredeemable Convertible Unsecured Loan Stock (ICULS)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sub-total of non-distributable reserves [Member]</t>
+          <t>Dividends paid</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital reserve [member]</t>
+          <t>Issuance of shares</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Foreign currency translation reserve [member]</t>
+          <t>Issue of convertible notes, net of tax</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Revaluation surplus [member]</t>
+          <t>Increase (decrease) through share-based payment transactions, equity</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Other non-distributable reserves [member]</t>
+          <t>Treasury shares transactions</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Other distributable reserves [member]</t>
+          <t>Other transactions with owners</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Equity, others components [member]</t>
+          <t>Increase (decrease) through other changes, equity</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Non-controlling interests [member]</t>
-        </is>
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>*Total increase (decrease) in equity</t>
+        </is>
+      </c>
+      <c r="B24">
+        <f>1*B13+1*B15+1*B16+-1*B17+1*B18+1*B19+1*B20+1*B21+1*B22+1*B23</f>
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Statement of changes in equity [line items]</t>
+          <t>Equity at end of period</t>
         </is>
       </c>
     </row>
@@ -594,154 +616,162 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Disclosure of changes in equity [abstract]</t>
+          <t>Disclosure of changes in equity</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Statement of changes in equity [abstract]</t>
+          <t>Statement of changes in equity</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Statement of changes in equity [table]</t>
+          <t>Equity at beginning of period</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Consolidated and separate financial statements [axis]</t>
+          <t>Impact of changes in accounting policies</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Group [member]</t>
+          <t>Equity at beginning of period, restated</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Company [member]</t>
+          <t>Changes in equity</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Components of equity [axis]</t>
+          <t>Comprehensive income</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Equity [member]</t>
+          <t>Profit (loss)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Equity attributable to owners of parent [member]</t>
+          <t>Total other comprehensive income</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Issued capital [member]</t>
-        </is>
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>*Total comprehensive income</t>
+        </is>
+      </c>
+      <c r="B37">
+        <f>1*B35+1*B36</f>
+        <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Retained earnings [member]</t>
+          <t>Contributions by and distributions to owners</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Treasury shares [member]</t>
+          <t>Acquisition (dilution) of equity interest in subsidiaries</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Reserves [Member]</t>
+          <t>Arising from conversion of Irredeemable Convertible Unsecured Loan Stock (ICULS)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sub-total of non-distributable reserves [Member]</t>
+          <t>Dividends paid</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Capital reserve [member]</t>
+          <t>Issuance of shares</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Foreign currency translation reserve [member]</t>
+          <t>Issue of convertible notes, net of tax</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Revaluation surplus [member]</t>
+          <t>Increase (decrease) through share-based payment transactions, equity</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Other non-distributable reserves [member]</t>
+          <t>Treasury shares transactions</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Other distributable reserves [member]</t>
+          <t>Other transactions with owners</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Equity, others components [member]</t>
+          <t>Increase (decrease) through other changes, equity</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Non-controlling interests [member]</t>
-        </is>
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>*Total increase (decrease) in equity</t>
+        </is>
+      </c>
+      <c r="B48">
+        <f>1*B37+1*B39+1*B40+-1*B41+1*B42+1*B43+1*B44+1*B45+1*B46+1*B47</f>
+        <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>Statement of changes in equity [line items]</t>
+          <t>Equity at end of period</t>
         </is>
       </c>
     </row>
@@ -755,154 +785,162 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Disclosure of changes in equity [abstract]</t>
+          <t>Disclosure of changes in equity</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Statement of changes in equity [abstract]</t>
+          <t>Statement of changes in equity</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Statement of changes in equity [table]</t>
+          <t>Equity at beginning of period</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Consolidated and separate financial statements [axis]</t>
+          <t>Impact of changes in accounting policies</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Group [member]</t>
+          <t>Equity at beginning of period, restated</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Company [member]</t>
+          <t>Changes in equity</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Components of equity [axis]</t>
+          <t>Comprehensive income</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Equity [member]</t>
+          <t>Profit (loss)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Equity attributable to owners of parent [member]</t>
+          <t>Total other comprehensive income</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Issued capital [member]</t>
-        </is>
+      <c r="A61" s="1" t="inlineStr">
+        <is>
+          <t>*Total comprehensive income</t>
+        </is>
+      </c>
+      <c r="B61">
+        <f>1*B59+1*B60</f>
+        <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Retained earnings [member]</t>
+          <t>Contributions by and distributions to owners</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Treasury shares [member]</t>
+          <t>Acquisition (dilution) of equity interest in subsidiaries</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Reserves [Member]</t>
+          <t>Arising from conversion of Irredeemable Convertible Unsecured Loan Stock (ICULS)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sub-total of non-distributable reserves [Member]</t>
+          <t>Dividends paid</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Capital reserve [member]</t>
+          <t>Issuance of shares</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Foreign currency translation reserve [member]</t>
+          <t>Issue of convertible notes, net of tax</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Revaluation surplus [member]</t>
+          <t>Increase (decrease) through share-based payment transactions, equity</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Other non-distributable reserves [member]</t>
+          <t>Treasury shares transactions</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Other distributable reserves [member]</t>
+          <t>Other transactions with owners</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Equity, others components [member]</t>
+          <t>Increase (decrease) through other changes, equity</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Non-controlling interests [member]</t>
-        </is>
+      <c r="A72" s="1" t="inlineStr">
+        <is>
+          <t>*Total increase (decrease) in equity</t>
+        </is>
+      </c>
+      <c r="B72">
+        <f>1*B61+1*B63+1*B64+-1*B65+1*B66+1*B67+1*B68+1*B69+1*B70+1*B71</f>
+        <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>Statement of changes in equity [line items]</t>
+          <t>Equity at end of period</t>
         </is>
       </c>
     </row>
@@ -916,154 +954,162 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Disclosure of changes in equity [abstract]</t>
+          <t>Disclosure of changes in equity</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Statement of changes in equity [abstract]</t>
+          <t>Statement of changes in equity</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Statement of changes in equity [table]</t>
+          <t>Equity at beginning of period</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Consolidated and separate financial statements [axis]</t>
+          <t>Impact of changes in accounting policies</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Group [member]</t>
+          <t>Equity at beginning of period, restated</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Company [member]</t>
+          <t>Changes in equity</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Components of equity [axis]</t>
+          <t>Comprehensive income</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Equity [member]</t>
+          <t>Profit (loss)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Equity attributable to owners of parent [member]</t>
+          <t>Total other comprehensive income</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Issued capital [member]</t>
-        </is>
+      <c r="A85" s="1" t="inlineStr">
+        <is>
+          <t>*Total comprehensive income</t>
+        </is>
+      </c>
+      <c r="B85">
+        <f>1*B83+1*B84</f>
+        <v/>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Retained earnings [member]</t>
+          <t>Contributions by and distributions to owners</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Treasury shares [member]</t>
+          <t>Acquisition (dilution) of equity interest in subsidiaries</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Reserves [Member]</t>
+          <t>Arising from conversion of Irredeemable Convertible Unsecured Loan Stock (ICULS)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Sub-total of non-distributable reserves [Member]</t>
+          <t>Dividends paid</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Capital reserve [member]</t>
+          <t>Issuance of shares</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Foreign currency translation reserve [member]</t>
+          <t>Issue of convertible notes, net of tax</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Revaluation surplus [member]</t>
+          <t>Increase (decrease) through share-based payment transactions, equity</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Other non-distributable reserves [member]</t>
+          <t>Treasury shares transactions</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Other distributable reserves [member]</t>
+          <t>Other transactions with owners</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Equity, others components [member]</t>
+          <t>Increase (decrease) through other changes, equity</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Non-controlling interests [member]</t>
-        </is>
+      <c r="A96" s="1" t="inlineStr">
+        <is>
+          <t>*Total increase (decrease) in equity</t>
+        </is>
+      </c>
+      <c r="B96">
+        <f>1*B85+1*B87+1*B88+-1*B89+1*B90+1*B91+1*B92+1*B93+1*B94+1*B95</f>
+        <v/>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>Statement of changes in equity [line items]</t>
+          <t>Equity at end of period</t>
         </is>
       </c>
     </row>
